--- a/artfynd/A 28734-2024 artfynd.xlsx
+++ b/artfynd/A 28734-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119536812</v>
+        <v>119536923</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533451</v>
+        <v>533284</v>
       </c>
       <c r="R2" t="n">
-        <v>7209465</v>
+        <v>7209569</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119536923</v>
+        <v>119536922</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533284</v>
+        <v>533270</v>
       </c>
       <c r="R3" t="n">
-        <v>7209569</v>
+        <v>7209571</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119536922</v>
+        <v>119536953</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533270</v>
+        <v>533577</v>
       </c>
       <c r="R4" t="n">
-        <v>7209571</v>
+        <v>7209380</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536953</v>
+        <v>119536812</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533577</v>
+        <v>533451</v>
       </c>
       <c r="R5" t="n">
-        <v>7209380</v>
+        <v>7209465</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536698</v>
+        <v>119536500</v>
       </c>
       <c r="B15" t="n">
-        <v>77463</v>
+        <v>90846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533259</v>
+        <v>533517</v>
       </c>
       <c r="R15" t="n">
-        <v>7209554</v>
+        <v>7209435</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536500</v>
+        <v>119536747</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533517</v>
+        <v>533286</v>
       </c>
       <c r="R16" t="n">
-        <v>7209435</v>
+        <v>7209570</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536747</v>
+        <v>119536009</v>
       </c>
       <c r="B17" t="n">
-        <v>78608</v>
+        <v>90562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533286</v>
+        <v>533480</v>
       </c>
       <c r="R17" t="n">
-        <v>7209570</v>
+        <v>7209465</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536009</v>
+        <v>119536769</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>90558</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533480</v>
+        <v>533560</v>
       </c>
       <c r="R18" t="n">
-        <v>7209465</v>
+        <v>7209301</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536769</v>
+        <v>119536353</v>
       </c>
       <c r="B19" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533560</v>
+        <v>533324</v>
       </c>
       <c r="R19" t="n">
-        <v>7209301</v>
+        <v>7209527</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536353</v>
+        <v>119536942</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533324</v>
+        <v>533471</v>
       </c>
       <c r="R20" t="n">
-        <v>7209527</v>
+        <v>7209472</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536942</v>
+        <v>119536940</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533471</v>
+        <v>533450</v>
       </c>
       <c r="R21" t="n">
-        <v>7209472</v>
+        <v>7209464</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536940</v>
+        <v>119537132</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,20 +2927,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533450</v>
+        <v>533301</v>
       </c>
       <c r="R22" t="n">
-        <v>7209464</v>
+        <v>7209573</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119537132</v>
+        <v>119536046</v>
       </c>
       <c r="B23" t="n">
-        <v>79642</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,38 +3039,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533301</v>
+        <v>533222</v>
       </c>
       <c r="R23" t="n">
-        <v>7209573</v>
+        <v>7209557</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536046</v>
+        <v>119536807</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,39 +3160,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533222</v>
+        <v>533245</v>
       </c>
       <c r="R24" t="n">
-        <v>7209557</v>
+        <v>7209553</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536807</v>
+        <v>119536698</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>77463</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,21 +3272,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533245</v>
+        <v>533259</v>
       </c>
       <c r="R25" t="n">
-        <v>7209553</v>
+        <v>7209554</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -6093,10 +6093,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536701</v>
+        <v>119536954</v>
       </c>
       <c r="B50" t="n">
-        <v>77867</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6105,25 +6105,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533263</v>
+        <v>533574</v>
       </c>
       <c r="R50" t="n">
-        <v>7209574</v>
+        <v>7209344</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6205,10 +6205,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119536011</v>
+        <v>119536943</v>
       </c>
       <c r="B51" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6221,21 +6221,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6245,10 +6245,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533572</v>
+        <v>533473</v>
       </c>
       <c r="R51" t="n">
-        <v>7209398</v>
+        <v>7209486</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6317,10 +6317,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119536474</v>
+        <v>119536038</v>
       </c>
       <c r="B52" t="n">
-        <v>74643</v>
+        <v>57310</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6333,34 +6333,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533343</v>
+        <v>533510</v>
       </c>
       <c r="R52" t="n">
-        <v>7209486</v>
+        <v>7209427</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6392,7 +6397,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6402,7 +6407,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6429,10 +6434,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119536954</v>
+        <v>119536701</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>77867</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6441,25 +6446,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6469,10 +6474,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533574</v>
+        <v>533263</v>
       </c>
       <c r="R53" t="n">
-        <v>7209344</v>
+        <v>7209574</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6504,7 +6509,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6514,7 +6519,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6541,10 +6546,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119536943</v>
+        <v>119536011</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6557,21 +6562,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6581,10 +6586,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533473</v>
+        <v>533572</v>
       </c>
       <c r="R54" t="n">
-        <v>7209486</v>
+        <v>7209398</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6616,7 +6621,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6626,7 +6631,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,10 +6658,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119536038</v>
+        <v>119536474</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>74643</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6669,39 +6674,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533510</v>
+        <v>533343</v>
       </c>
       <c r="R55" t="n">
-        <v>7209427</v>
+        <v>7209486</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8012,10 +8012,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119536749</v>
+        <v>119536809</v>
       </c>
       <c r="B67" t="n">
-        <v>78608</v>
+        <v>90580</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8028,21 +8028,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533323</v>
+        <v>533337</v>
       </c>
       <c r="R67" t="n">
-        <v>7209527</v>
+        <v>7209483</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8124,10 +8124,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119536926</v>
+        <v>119536749</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>78608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8140,21 +8140,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8164,10 +8164,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533325</v>
+        <v>533323</v>
       </c>
       <c r="R68" t="n">
-        <v>7209530</v>
+        <v>7209527</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8236,7 +8236,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119536919</v>
+        <v>119536926</v>
       </c>
       <c r="B69" t="n">
         <v>78526</v>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533261</v>
+        <v>533325</v>
       </c>
       <c r="R69" t="n">
-        <v>7209575</v>
+        <v>7209530</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8348,7 +8348,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119536960</v>
+        <v>119536919</v>
       </c>
       <c r="B70" t="n">
         <v>78526</v>
@@ -8388,10 +8388,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533570</v>
+        <v>533261</v>
       </c>
       <c r="R70" t="n">
-        <v>7209329</v>
+        <v>7209575</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8460,7 +8460,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119536964</v>
+        <v>119536960</v>
       </c>
       <c r="B71" t="n">
         <v>78526</v>
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533550</v>
+        <v>533570</v>
       </c>
       <c r="R71" t="n">
-        <v>7209252</v>
+        <v>7209329</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8572,10 +8572,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119536809</v>
+        <v>119536964</v>
       </c>
       <c r="B72" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8588,21 +8588,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8612,10 +8612,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533337</v>
+        <v>533550</v>
       </c>
       <c r="R72" t="n">
-        <v>7209483</v>
+        <v>7209252</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8684,10 +8684,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119536508</v>
+        <v>119536808</v>
       </c>
       <c r="B73" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8700,34 +8700,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533584</v>
+        <v>533271</v>
       </c>
       <c r="R73" t="n">
-        <v>7209318</v>
+        <v>7209571</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8759,7 +8762,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8772,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8778,6 +8781,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8796,7 +8800,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119536506</v>
+        <v>119536508</v>
       </c>
       <c r="B74" t="n">
         <v>90846</v>
@@ -8836,10 +8840,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533574</v>
+        <v>533584</v>
       </c>
       <c r="R74" t="n">
-        <v>7209341</v>
+        <v>7209318</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8871,7 +8875,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8881,7 +8885,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8908,10 +8912,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119536808</v>
+        <v>119536506</v>
       </c>
       <c r="B75" t="n">
-        <v>90580</v>
+        <v>90846</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8924,37 +8928,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533271</v>
+        <v>533574</v>
       </c>
       <c r="R75" t="n">
-        <v>7209571</v>
+        <v>7209341</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8986,7 +8987,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8997,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9005,7 +9006,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -11059,10 +11059,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119536502</v>
+        <v>119536552</v>
       </c>
       <c r="B94" t="n">
-        <v>90846</v>
+        <v>96868</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11071,25 +11071,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533517</v>
+        <v>533466</v>
       </c>
       <c r="R94" t="n">
-        <v>7209427</v>
+        <v>7209280</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11171,10 +11171,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119536766</v>
+        <v>119536708</v>
       </c>
       <c r="B95" t="n">
-        <v>90558</v>
+        <v>57459</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11187,34 +11187,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1108</v>
+        <v>103022</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533470</v>
+        <v>533244</v>
       </c>
       <c r="R95" t="n">
-        <v>7209486</v>
+        <v>7209556</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11246,7 +11250,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11256,7 +11260,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11283,10 +11287,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119537032</v>
+        <v>119536502</v>
       </c>
       <c r="B96" t="n">
-        <v>82305</v>
+        <v>90846</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11299,21 +11303,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11323,10 +11327,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533575</v>
+        <v>533517</v>
       </c>
       <c r="R96" t="n">
-        <v>7209338</v>
+        <v>7209427</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11358,7 +11362,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11368,7 +11372,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11395,10 +11399,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119536473</v>
+        <v>119536766</v>
       </c>
       <c r="B97" t="n">
-        <v>74643</v>
+        <v>90558</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11411,21 +11415,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11435,10 +11439,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533314</v>
+        <v>533470</v>
       </c>
       <c r="R97" t="n">
-        <v>7209484</v>
+        <v>7209486</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11470,7 +11474,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11480,7 +11484,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11507,10 +11511,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119536750</v>
+        <v>119537032</v>
       </c>
       <c r="B98" t="n">
-        <v>78608</v>
+        <v>82305</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11523,21 +11527,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11550,7 +11554,7 @@
         <v>533575</v>
       </c>
       <c r="R98" t="n">
-        <v>7209381</v>
+        <v>7209338</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11582,7 +11586,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11592,7 +11596,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11619,10 +11623,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119536793</v>
+        <v>119536473</v>
       </c>
       <c r="B99" t="n">
-        <v>90576</v>
+        <v>74643</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11635,21 +11639,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11659,10 +11663,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533574</v>
+        <v>533314</v>
       </c>
       <c r="R99" t="n">
-        <v>7209340</v>
+        <v>7209484</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11694,7 +11698,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11704,7 +11708,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11731,10 +11735,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119536351</v>
+        <v>119536750</v>
       </c>
       <c r="B100" t="n">
-        <v>79608</v>
+        <v>78608</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11747,21 +11751,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11771,10 +11775,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533312</v>
+        <v>533575</v>
       </c>
       <c r="R100" t="n">
-        <v>7209566</v>
+        <v>7209381</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11806,7 +11810,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11816,7 +11820,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11843,10 +11847,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119536620</v>
+        <v>119536793</v>
       </c>
       <c r="B101" t="n">
-        <v>94311</v>
+        <v>90576</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11855,25 +11859,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2809</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11883,10 +11887,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533469</v>
+        <v>533574</v>
       </c>
       <c r="R101" t="n">
-        <v>7209480</v>
+        <v>7209340</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11918,7 +11922,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11928,7 +11932,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11955,10 +11959,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119537135</v>
+        <v>119536351</v>
       </c>
       <c r="B102" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11967,25 +11971,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11995,10 +11999,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533547</v>
+        <v>533312</v>
       </c>
       <c r="R102" t="n">
-        <v>7209254</v>
+        <v>7209566</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12030,7 +12034,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12040,7 +12044,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12067,10 +12071,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119535984</v>
+        <v>119536620</v>
       </c>
       <c r="B103" t="n">
-        <v>90527</v>
+        <v>94311</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12083,21 +12087,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12107,10 +12111,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533391</v>
+        <v>533469</v>
       </c>
       <c r="R103" t="n">
-        <v>7209501</v>
+        <v>7209480</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12142,7 +12146,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12152,7 +12156,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12403,10 +12407,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119536552</v>
+        <v>119537135</v>
       </c>
       <c r="B106" t="n">
-        <v>96868</v>
+        <v>79642</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12419,21 +12423,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12443,10 +12447,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533466</v>
+        <v>533547</v>
       </c>
       <c r="R106" t="n">
-        <v>7209280</v>
+        <v>7209254</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12478,7 +12482,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12488,7 +12492,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12515,10 +12519,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119536708</v>
+        <v>119535984</v>
       </c>
       <c r="B107" t="n">
-        <v>57459</v>
+        <v>90527</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12527,42 +12531,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103022</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533244</v>
+        <v>533391</v>
       </c>
       <c r="R107" t="n">
-        <v>7209556</v>
+        <v>7209501</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13308,10 +13308,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119536921</v>
+        <v>119536404</v>
       </c>
       <c r="B114" t="n">
-        <v>78526</v>
+        <v>94323</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13320,25 +13320,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13348,10 +13348,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533273</v>
+        <v>533574</v>
       </c>
       <c r="R114" t="n">
-        <v>7209584</v>
+        <v>7209378</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13420,7 +13420,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119536920</v>
+        <v>119536921</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533266</v>
+        <v>533273</v>
       </c>
       <c r="R115" t="n">
-        <v>7209576</v>
+        <v>7209584</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13532,7 +13532,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119536955</v>
+        <v>119536920</v>
       </c>
       <c r="B116" t="n">
         <v>78526</v>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533595</v>
+        <v>533266</v>
       </c>
       <c r="R116" t="n">
-        <v>7209370</v>
+        <v>7209576</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13644,7 +13644,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119536968</v>
+        <v>119536955</v>
       </c>
       <c r="B117" t="n">
         <v>78526</v>
@@ -13684,10 +13684,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533495</v>
+        <v>533595</v>
       </c>
       <c r="R117" t="n">
-        <v>7209258</v>
+        <v>7209370</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13756,7 +13756,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119536933</v>
+        <v>119536968</v>
       </c>
       <c r="B118" t="n">
         <v>78526</v>
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533413</v>
+        <v>533495</v>
       </c>
       <c r="R118" t="n">
-        <v>7209495</v>
+        <v>7209258</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13868,10 +13868,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119536404</v>
+        <v>119536933</v>
       </c>
       <c r="B119" t="n">
-        <v>94323</v>
+        <v>78526</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13880,25 +13880,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533574</v>
+        <v>533413</v>
       </c>
       <c r="R119" t="n">
-        <v>7209378</v>
+        <v>7209495</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13980,10 +13980,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119536247</v>
+        <v>119536702</v>
       </c>
       <c r="B120" t="n">
-        <v>91339</v>
+        <v>77867</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13996,21 +13996,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>918</v>
+        <v>498</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14020,10 +14020,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533337</v>
+        <v>533548</v>
       </c>
       <c r="R120" t="n">
-        <v>7209483</v>
+        <v>7209249</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14092,10 +14092,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119536957</v>
+        <v>119536616</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>74633</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14108,21 +14108,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14132,10 +14132,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533575</v>
+        <v>533429</v>
       </c>
       <c r="R121" t="n">
-        <v>7209339</v>
+        <v>7209490</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14204,10 +14204,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119536962</v>
+        <v>119536247</v>
       </c>
       <c r="B122" t="n">
-        <v>78526</v>
+        <v>91339</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>918</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533550</v>
+        <v>533337</v>
       </c>
       <c r="R122" t="n">
-        <v>7209319</v>
+        <v>7209483</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14316,7 +14316,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119536941</v>
+        <v>119536957</v>
       </c>
       <c r="B123" t="n">
         <v>78526</v>
@@ -14356,10 +14356,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533469</v>
+        <v>533575</v>
       </c>
       <c r="R123" t="n">
-        <v>7209454</v>
+        <v>7209339</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14428,10 +14428,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119536031</v>
+        <v>119536962</v>
       </c>
       <c r="B124" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14444,39 +14444,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>533438</v>
+        <v>533550</v>
       </c>
       <c r="R124" t="n">
-        <v>7209488</v>
+        <v>7209319</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14508,7 +14503,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14518,7 +14513,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14545,10 +14540,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119536702</v>
+        <v>119536941</v>
       </c>
       <c r="B125" t="n">
-        <v>77867</v>
+        <v>78526</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14557,25 +14552,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14585,10 +14580,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533548</v>
+        <v>533469</v>
       </c>
       <c r="R125" t="n">
-        <v>7209249</v>
+        <v>7209454</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14620,7 +14615,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14630,7 +14625,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14657,10 +14652,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119536616</v>
+        <v>119536031</v>
       </c>
       <c r="B126" t="n">
-        <v>74633</v>
+        <v>57310</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14673,34 +14668,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>533429</v>
+        <v>533438</v>
       </c>
       <c r="R126" t="n">
-        <v>7209490</v>
+        <v>7209488</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14732,7 +14732,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14885,10 +14885,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119536938</v>
+        <v>119536794</v>
       </c>
       <c r="B128" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14901,21 +14901,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14925,10 +14925,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>533435</v>
+        <v>533582</v>
       </c>
       <c r="R128" t="n">
-        <v>7209492</v>
+        <v>7209319</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14997,10 +14997,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119536504</v>
+        <v>119536357</v>
       </c>
       <c r="B129" t="n">
-        <v>90846</v>
+        <v>79608</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15013,21 +15013,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15037,10 +15037,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533522</v>
+        <v>533575</v>
       </c>
       <c r="R129" t="n">
-        <v>7209433</v>
+        <v>7209351</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15109,10 +15109,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119536794</v>
+        <v>119536034</v>
       </c>
       <c r="B130" t="n">
-        <v>90576</v>
+        <v>57310</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15125,34 +15125,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533582</v>
+        <v>533494</v>
       </c>
       <c r="R130" t="n">
-        <v>7209319</v>
+        <v>7209504</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15184,7 +15189,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15194,7 +15199,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15221,10 +15226,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119536357</v>
+        <v>119536504</v>
       </c>
       <c r="B131" t="n">
-        <v>79608</v>
+        <v>90846</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15237,21 +15242,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15261,10 +15266,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533575</v>
+        <v>533522</v>
       </c>
       <c r="R131" t="n">
-        <v>7209351</v>
+        <v>7209433</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -15296,7 +15301,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15306,7 +15311,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15333,10 +15338,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119536034</v>
+        <v>119536938</v>
       </c>
       <c r="B132" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15349,39 +15354,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>533494</v>
+        <v>533435</v>
       </c>
       <c r="R132" t="n">
-        <v>7209504</v>
+        <v>7209492</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16906,10 +16906,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119537246</v>
+        <v>119536621</v>
       </c>
       <c r="B146" t="n">
-        <v>90957</v>
+        <v>94311</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16922,21 +16922,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4217</v>
+        <v>2809</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16946,10 +16946,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>533515</v>
+        <v>533574</v>
       </c>
       <c r="R146" t="n">
-        <v>7209438</v>
+        <v>7209376</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17002,21 +17002,6 @@
       </c>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -17033,10 +17018,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119536621</v>
+        <v>119536356</v>
       </c>
       <c r="B147" t="n">
-        <v>94311</v>
+        <v>79608</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17045,25 +17030,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17073,10 +17058,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>533574</v>
+        <v>533430</v>
       </c>
       <c r="R147" t="n">
-        <v>7209376</v>
+        <v>7209489</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17108,7 +17093,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17118,7 +17103,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17145,10 +17130,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119536356</v>
+        <v>119536918</v>
       </c>
       <c r="B148" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17161,21 +17146,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17185,10 +17170,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>533430</v>
+        <v>533256</v>
       </c>
       <c r="R148" t="n">
-        <v>7209489</v>
+        <v>7209556</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -17220,7 +17205,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17230,7 +17215,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17257,10 +17242,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119536918</v>
+        <v>119535970</v>
       </c>
       <c r="B149" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17273,21 +17258,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17297,10 +17282,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>533256</v>
+        <v>533258</v>
       </c>
       <c r="R149" t="n">
-        <v>7209556</v>
+        <v>7209555</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -17332,7 +17317,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17342,7 +17327,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17369,10 +17354,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119535970</v>
+        <v>119537246</v>
       </c>
       <c r="B150" t="n">
-        <v>74638</v>
+        <v>90957</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17381,25 +17366,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6440</v>
+        <v>4217</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17409,10 +17394,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>533258</v>
+        <v>533515</v>
       </c>
       <c r="R150" t="n">
-        <v>7209555</v>
+        <v>7209438</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -17444,7 +17429,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17454,7 +17439,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17465,6 +17450,21 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -17481,10 +17481,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119536944</v>
+        <v>119536045</v>
       </c>
       <c r="B151" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17497,34 +17497,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533517</v>
+        <v>533294</v>
       </c>
       <c r="R151" t="n">
-        <v>7209435</v>
+        <v>7209474</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -17556,7 +17561,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17566,7 +17571,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17593,7 +17598,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119536934</v>
+        <v>119536944</v>
       </c>
       <c r="B152" t="n">
         <v>78526</v>
@@ -17633,10 +17638,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533440</v>
+        <v>533517</v>
       </c>
       <c r="R152" t="n">
-        <v>7209514</v>
+        <v>7209435</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -17668,7 +17673,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17678,7 +17683,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17705,10 +17710,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119535971</v>
+        <v>119536934</v>
       </c>
       <c r="B153" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17721,21 +17726,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17745,10 +17750,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533287</v>
+        <v>533440</v>
       </c>
       <c r="R153" t="n">
-        <v>7209579</v>
+        <v>7209514</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -17780,7 +17785,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17790,7 +17795,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17817,10 +17822,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119536713</v>
+        <v>119535971</v>
       </c>
       <c r="B154" t="n">
-        <v>90954</v>
+        <v>74638</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17833,32 +17838,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533571</v>
+        <v>533287</v>
       </c>
       <c r="R154" t="n">
-        <v>7209397</v>
+        <v>7209579</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17890,7 +17897,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17900,7 +17907,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17909,7 +17916,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17928,10 +17934,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119536045</v>
+        <v>119536713</v>
       </c>
       <c r="B155" t="n">
-        <v>57310</v>
+        <v>90954</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17944,39 +17950,32 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533294</v>
+        <v>533571</v>
       </c>
       <c r="R155" t="n">
-        <v>7209474</v>
+        <v>7209397</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18008,7 +18007,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18018,7 +18017,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18027,6 +18026,7 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28734-2024 artfynd.xlsx
+++ b/artfynd/A 28734-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536963</v>
+        <v>119536555</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>90916</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533559</v>
+        <v>533414</v>
       </c>
       <c r="R6" t="n">
-        <v>7209301</v>
+        <v>7209496</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536961</v>
+        <v>119536012</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533584</v>
+        <v>533588</v>
       </c>
       <c r="R7" t="n">
-        <v>7209323</v>
+        <v>7209319</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536946</v>
+        <v>119536767</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533514</v>
+        <v>533577</v>
       </c>
       <c r="R8" t="n">
-        <v>7209425</v>
+        <v>7209333</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536958</v>
+        <v>119536748</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533572</v>
+        <v>533330</v>
       </c>
       <c r="R9" t="n">
-        <v>7209339</v>
+        <v>7209552</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536767</v>
+        <v>119536354</v>
       </c>
       <c r="B10" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533577</v>
+        <v>533360</v>
       </c>
       <c r="R10" t="n">
-        <v>7209333</v>
+        <v>7209461</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536748</v>
+        <v>119536963</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533330</v>
+        <v>533559</v>
       </c>
       <c r="R11" t="n">
-        <v>7209552</v>
+        <v>7209301</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536354</v>
+        <v>119536961</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533360</v>
+        <v>533584</v>
       </c>
       <c r="R12" t="n">
-        <v>7209461</v>
+        <v>7209323</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536555</v>
+        <v>119536946</v>
       </c>
       <c r="B13" t="n">
-        <v>90916</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533414</v>
+        <v>533514</v>
       </c>
       <c r="R13" t="n">
-        <v>7209496</v>
+        <v>7209425</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536012</v>
+        <v>119536958</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533588</v>
+        <v>533572</v>
       </c>
       <c r="R14" t="n">
-        <v>7209319</v>
+        <v>7209339</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -8684,10 +8684,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119536808</v>
+        <v>119536508</v>
       </c>
       <c r="B73" t="n">
-        <v>90580</v>
+        <v>90846</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8700,37 +8700,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533271</v>
+        <v>533584</v>
       </c>
       <c r="R73" t="n">
-        <v>7209571</v>
+        <v>7209318</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8762,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8772,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8781,7 +8778,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8800,7 +8796,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119536508</v>
+        <v>119536506</v>
       </c>
       <c r="B74" t="n">
         <v>90846</v>
@@ -8840,10 +8836,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533584</v>
+        <v>533574</v>
       </c>
       <c r="R74" t="n">
-        <v>7209318</v>
+        <v>7209341</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8875,7 +8871,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8885,7 +8881,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8912,10 +8908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119536506</v>
+        <v>119536808</v>
       </c>
       <c r="B75" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8928,34 +8924,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533574</v>
+        <v>533271</v>
       </c>
       <c r="R75" t="n">
-        <v>7209341</v>
+        <v>7209571</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8987,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8997,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9006,6 +9005,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -11059,10 +11059,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119536552</v>
+        <v>119536502</v>
       </c>
       <c r="B94" t="n">
-        <v>96868</v>
+        <v>90846</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11071,25 +11071,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533466</v>
+        <v>533517</v>
       </c>
       <c r="R94" t="n">
-        <v>7209280</v>
+        <v>7209427</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11171,10 +11171,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119536708</v>
+        <v>119536766</v>
       </c>
       <c r="B95" t="n">
-        <v>57459</v>
+        <v>90558</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11187,38 +11187,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103022</v>
+        <v>1108</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533244</v>
+        <v>533470</v>
       </c>
       <c r="R95" t="n">
-        <v>7209556</v>
+        <v>7209486</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11250,7 +11246,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11260,7 +11256,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11287,10 +11283,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119536502</v>
+        <v>119537032</v>
       </c>
       <c r="B96" t="n">
-        <v>90846</v>
+        <v>82305</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11303,21 +11299,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11327,10 +11323,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533517</v>
+        <v>533575</v>
       </c>
       <c r="R96" t="n">
-        <v>7209427</v>
+        <v>7209338</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11362,7 +11358,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11372,7 +11368,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11399,10 +11395,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119536766</v>
+        <v>119536473</v>
       </c>
       <c r="B97" t="n">
-        <v>90558</v>
+        <v>74643</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11415,21 +11411,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11439,10 +11435,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533470</v>
+        <v>533314</v>
       </c>
       <c r="R97" t="n">
-        <v>7209486</v>
+        <v>7209484</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11474,7 +11470,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11484,7 +11480,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11511,10 +11507,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119537032</v>
+        <v>119536750</v>
       </c>
       <c r="B98" t="n">
-        <v>82305</v>
+        <v>78608</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11527,21 +11523,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11554,7 +11550,7 @@
         <v>533575</v>
       </c>
       <c r="R98" t="n">
-        <v>7209338</v>
+        <v>7209381</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11586,7 +11582,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11596,7 +11592,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11623,10 +11619,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119536473</v>
+        <v>119536793</v>
       </c>
       <c r="B99" t="n">
-        <v>74643</v>
+        <v>90576</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11639,21 +11635,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11663,10 +11659,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533314</v>
+        <v>533574</v>
       </c>
       <c r="R99" t="n">
-        <v>7209484</v>
+        <v>7209340</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11698,7 +11694,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11708,7 +11704,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11735,10 +11731,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119536750</v>
+        <v>119536351</v>
       </c>
       <c r="B100" t="n">
-        <v>78608</v>
+        <v>79608</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11751,21 +11747,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11775,10 +11771,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533575</v>
+        <v>533312</v>
       </c>
       <c r="R100" t="n">
-        <v>7209381</v>
+        <v>7209566</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11810,7 +11806,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11820,7 +11816,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11847,10 +11843,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119536793</v>
+        <v>119536620</v>
       </c>
       <c r="B101" t="n">
-        <v>90576</v>
+        <v>94311</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11859,25 +11855,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>2809</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11887,10 +11883,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533574</v>
+        <v>533469</v>
       </c>
       <c r="R101" t="n">
-        <v>7209340</v>
+        <v>7209480</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11922,7 +11918,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11932,7 +11928,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11959,10 +11955,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119536351</v>
+        <v>119537135</v>
       </c>
       <c r="B102" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11971,25 +11967,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11999,10 +11995,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533312</v>
+        <v>533547</v>
       </c>
       <c r="R102" t="n">
-        <v>7209566</v>
+        <v>7209254</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12034,7 +12030,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12044,7 +12040,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12071,10 +12067,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119536620</v>
+        <v>119535984</v>
       </c>
       <c r="B103" t="n">
-        <v>94311</v>
+        <v>90527</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12087,21 +12083,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12111,10 +12107,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533469</v>
+        <v>533391</v>
       </c>
       <c r="R103" t="n">
-        <v>7209480</v>
+        <v>7209501</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12146,7 +12142,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12156,7 +12152,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12407,10 +12403,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119537135</v>
+        <v>119536552</v>
       </c>
       <c r="B106" t="n">
-        <v>79642</v>
+        <v>96868</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12423,21 +12419,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12447,10 +12443,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533547</v>
+        <v>533466</v>
       </c>
       <c r="R106" t="n">
-        <v>7209254</v>
+        <v>7209280</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12482,7 +12478,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12492,7 +12488,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12519,10 +12515,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119535984</v>
+        <v>119536708</v>
       </c>
       <c r="B107" t="n">
-        <v>90527</v>
+        <v>57459</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12531,38 +12527,42 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>103022</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533391</v>
+        <v>533244</v>
       </c>
       <c r="R107" t="n">
-        <v>7209501</v>
+        <v>7209556</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13980,10 +13980,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119536702</v>
+        <v>119536247</v>
       </c>
       <c r="B120" t="n">
-        <v>77867</v>
+        <v>91339</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13996,21 +13996,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>498</v>
+        <v>918</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14020,10 +14020,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533548</v>
+        <v>533337</v>
       </c>
       <c r="R120" t="n">
-        <v>7209249</v>
+        <v>7209483</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14092,10 +14092,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119536616</v>
+        <v>119536957</v>
       </c>
       <c r="B121" t="n">
-        <v>74633</v>
+        <v>78526</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14108,21 +14108,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14132,10 +14132,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533429</v>
+        <v>533575</v>
       </c>
       <c r="R121" t="n">
-        <v>7209490</v>
+        <v>7209339</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14204,10 +14204,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119536247</v>
+        <v>119536962</v>
       </c>
       <c r="B122" t="n">
-        <v>91339</v>
+        <v>78526</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14216,25 +14216,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>918</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533337</v>
+        <v>533550</v>
       </c>
       <c r="R122" t="n">
-        <v>7209483</v>
+        <v>7209319</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14316,7 +14316,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119536957</v>
+        <v>119536941</v>
       </c>
       <c r="B123" t="n">
         <v>78526</v>
@@ -14356,10 +14356,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533575</v>
+        <v>533469</v>
       </c>
       <c r="R123" t="n">
-        <v>7209339</v>
+        <v>7209454</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14428,10 +14428,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119536962</v>
+        <v>119536031</v>
       </c>
       <c r="B124" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14444,34 +14444,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>533550</v>
+        <v>533438</v>
       </c>
       <c r="R124" t="n">
-        <v>7209319</v>
+        <v>7209488</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14503,7 +14508,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14513,7 +14518,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14540,10 +14545,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119536941</v>
+        <v>119536702</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>77867</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14552,25 +14557,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14580,10 +14585,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533469</v>
+        <v>533548</v>
       </c>
       <c r="R125" t="n">
-        <v>7209454</v>
+        <v>7209249</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14615,7 +14620,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14625,7 +14630,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14652,10 +14657,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119536031</v>
+        <v>119536616</v>
       </c>
       <c r="B126" t="n">
-        <v>57310</v>
+        <v>74633</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14668,39 +14673,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>533438</v>
+        <v>533429</v>
       </c>
       <c r="R126" t="n">
-        <v>7209488</v>
+        <v>7209490</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14732,7 +14732,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14885,10 +14885,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119536794</v>
+        <v>119536938</v>
       </c>
       <c r="B128" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14901,21 +14901,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14925,10 +14925,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>533582</v>
+        <v>533435</v>
       </c>
       <c r="R128" t="n">
-        <v>7209319</v>
+        <v>7209492</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14997,10 +14997,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119536357</v>
+        <v>119536504</v>
       </c>
       <c r="B129" t="n">
-        <v>79608</v>
+        <v>90846</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15013,21 +15013,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15037,10 +15037,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533575</v>
+        <v>533522</v>
       </c>
       <c r="R129" t="n">
-        <v>7209351</v>
+        <v>7209433</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15109,10 +15109,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119536034</v>
+        <v>119536794</v>
       </c>
       <c r="B130" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15125,39 +15125,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533494</v>
+        <v>533582</v>
       </c>
       <c r="R130" t="n">
-        <v>7209504</v>
+        <v>7209319</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15189,7 +15184,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15199,7 +15194,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15226,10 +15221,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119536504</v>
+        <v>119536357</v>
       </c>
       <c r="B131" t="n">
-        <v>90846</v>
+        <v>79608</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15242,21 +15237,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15266,10 +15261,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533522</v>
+        <v>533575</v>
       </c>
       <c r="R131" t="n">
-        <v>7209433</v>
+        <v>7209351</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -15301,7 +15296,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15311,7 +15306,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15338,10 +15333,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119536938</v>
+        <v>119536034</v>
       </c>
       <c r="B132" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15354,34 +15349,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>533435</v>
+        <v>533494</v>
       </c>
       <c r="R132" t="n">
-        <v>7209492</v>
+        <v>7209504</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD132" t="b">

--- a/artfynd/A 28734-2024 artfynd.xlsx
+++ b/artfynd/A 28734-2024 artfynd.xlsx
@@ -2491,10 +2491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536090</v>
+        <v>119535984</v>
       </c>
       <c r="B18" t="n">
-        <v>56572</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,47 +2503,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102976</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533477</v>
+        <v>533391</v>
       </c>
       <c r="R18" t="n">
-        <v>7209483</v>
+        <v>7209501</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2575,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119535984</v>
+        <v>119536939</v>
       </c>
       <c r="B19" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,25 +2615,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2652,10 +2643,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533391</v>
+        <v>533458</v>
       </c>
       <c r="R19" t="n">
-        <v>7209501</v>
+        <v>7209468</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,7 +2678,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2688,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3060,10 +3051,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536939</v>
+        <v>119536090</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>56572</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,38 +3063,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533458</v>
+        <v>533477</v>
       </c>
       <c r="R23" t="n">
-        <v>7209468</v>
+        <v>7209483</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119537246</v>
+        <v>119536621</v>
       </c>
       <c r="B26" t="n">
-        <v>90957</v>
+        <v>94311</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4217</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533515</v>
+        <v>533574</v>
       </c>
       <c r="R26" t="n">
-        <v>7209438</v>
+        <v>7209376</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3492,21 +3492,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3523,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536621</v>
+        <v>119537246</v>
       </c>
       <c r="B27" t="n">
-        <v>94311</v>
+        <v>90957</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3539,21 +3524,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>4217</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3563,10 +3548,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533574</v>
+        <v>533515</v>
       </c>
       <c r="R27" t="n">
-        <v>7209376</v>
+        <v>7209438</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3598,7 +3583,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3608,7 +3593,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,6 +3604,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4307,10 +4307,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536968</v>
+        <v>119536766</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533495</v>
+        <v>533470</v>
       </c>
       <c r="R34" t="n">
-        <v>7209258</v>
+        <v>7209486</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536808</v>
+        <v>119536968</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4435,37 +4435,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533271</v>
+        <v>533495</v>
       </c>
       <c r="R35" t="n">
-        <v>7209571</v>
+        <v>7209258</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4497,7 +4494,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4507,7 +4504,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4516,7 +4513,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4535,10 +4531,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536813</v>
+        <v>119536768</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4551,21 +4547,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4575,10 +4571,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533541</v>
+        <v>533552</v>
       </c>
       <c r="R36" t="n">
-        <v>7209434</v>
+        <v>7209317</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4610,7 +4606,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4620,7 +4616,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4647,7 +4643,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536768</v>
+        <v>119536767</v>
       </c>
       <c r="B37" t="n">
         <v>90558</v>
@@ -4687,10 +4683,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533552</v>
+        <v>533577</v>
       </c>
       <c r="R37" t="n">
-        <v>7209317</v>
+        <v>7209333</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4722,7 +4718,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4732,7 +4728,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4759,10 +4755,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536767</v>
+        <v>119536808</v>
       </c>
       <c r="B38" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4775,34 +4771,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533577</v>
+        <v>533271</v>
       </c>
       <c r="R38" t="n">
-        <v>7209333</v>
+        <v>7209571</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4834,7 +4833,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4844,7 +4843,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4853,6 +4852,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4871,10 +4871,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536920</v>
+        <v>119536813</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4887,21 +4887,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533266</v>
+        <v>533541</v>
       </c>
       <c r="R39" t="n">
-        <v>7209576</v>
+        <v>7209434</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4983,10 +4983,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536766</v>
+        <v>119536920</v>
       </c>
       <c r="B40" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533470</v>
+        <v>533266</v>
       </c>
       <c r="R40" t="n">
-        <v>7209486</v>
+        <v>7209576</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5095,10 +5095,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536349</v>
+        <v>119536919</v>
       </c>
       <c r="B41" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5111,21 +5111,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533241</v>
+        <v>533261</v>
       </c>
       <c r="R41" t="n">
-        <v>7209552</v>
+        <v>7209575</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5207,10 +5207,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536009</v>
+        <v>119536349</v>
       </c>
       <c r="B42" t="n">
-        <v>90562</v>
+        <v>79608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5223,21 +5223,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533480</v>
+        <v>533241</v>
       </c>
       <c r="R42" t="n">
-        <v>7209465</v>
+        <v>7209552</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5319,10 +5319,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536404</v>
+        <v>119536009</v>
       </c>
       <c r="B43" t="n">
-        <v>94323</v>
+        <v>90562</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533574</v>
+        <v>533480</v>
       </c>
       <c r="R43" t="n">
-        <v>7209378</v>
+        <v>7209465</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536919</v>
+        <v>119536404</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>94323</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533261</v>
+        <v>533574</v>
       </c>
       <c r="R44" t="n">
-        <v>7209575</v>
+        <v>7209378</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6785,10 +6785,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119536012</v>
+        <v>119536747</v>
       </c>
       <c r="B56" t="n">
-        <v>90562</v>
+        <v>78608</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6801,21 +6801,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533588</v>
+        <v>533286</v>
       </c>
       <c r="R56" t="n">
-        <v>7209319</v>
+        <v>7209570</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6897,10 +6897,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119537034</v>
+        <v>119536504</v>
       </c>
       <c r="B57" t="n">
-        <v>82305</v>
+        <v>90846</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6913,21 +6913,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6937,10 +6937,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533550</v>
+        <v>533522</v>
       </c>
       <c r="R57" t="n">
-        <v>7209253</v>
+        <v>7209433</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7009,10 +7009,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119537031</v>
+        <v>119536950</v>
       </c>
       <c r="B58" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7025,21 +7025,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533574</v>
+        <v>533558</v>
       </c>
       <c r="R58" t="n">
-        <v>7209384</v>
+        <v>7209426</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7121,10 +7121,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119536504</v>
+        <v>119536965</v>
       </c>
       <c r="B59" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7137,21 +7137,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533522</v>
+        <v>533545</v>
       </c>
       <c r="R59" t="n">
-        <v>7209433</v>
+        <v>7209289</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7233,10 +7233,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119536965</v>
+        <v>119536698</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>77463</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7249,21 +7249,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7273,10 +7273,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533545</v>
+        <v>533259</v>
       </c>
       <c r="R60" t="n">
-        <v>7209289</v>
+        <v>7209554</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7345,10 +7345,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119536747</v>
+        <v>119536012</v>
       </c>
       <c r="B61" t="n">
-        <v>78608</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7361,21 +7361,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533286</v>
+        <v>533588</v>
       </c>
       <c r="R61" t="n">
-        <v>7209570</v>
+        <v>7209319</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7457,10 +7457,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119536950</v>
+        <v>119537034</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7473,21 +7473,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533558</v>
+        <v>533550</v>
       </c>
       <c r="R62" t="n">
-        <v>7209426</v>
+        <v>7209253</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7569,10 +7569,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119536698</v>
+        <v>119537031</v>
       </c>
       <c r="B63" t="n">
-        <v>77463</v>
+        <v>82305</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7585,21 +7585,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533259</v>
+        <v>533574</v>
       </c>
       <c r="R63" t="n">
-        <v>7209554</v>
+        <v>7209384</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7798,10 +7798,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119536522</v>
+        <v>119536686</v>
       </c>
       <c r="B65" t="n">
-        <v>96862</v>
+        <v>79643</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533570</v>
+        <v>533432</v>
       </c>
       <c r="R65" t="n">
-        <v>7209339</v>
+        <v>7209492</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7910,10 +7910,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119536620</v>
+        <v>119536687</v>
       </c>
       <c r="B66" t="n">
-        <v>94311</v>
+        <v>79643</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7926,21 +7926,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533469</v>
+        <v>533574</v>
       </c>
       <c r="R66" t="n">
-        <v>7209480</v>
+        <v>7209350</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8022,10 +8022,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119536922</v>
+        <v>119536620</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>94311</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8034,25 +8034,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533270</v>
+        <v>533469</v>
       </c>
       <c r="R67" t="n">
-        <v>7209571</v>
+        <v>7209480</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8134,7 +8134,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119536961</v>
+        <v>119536922</v>
       </c>
       <c r="B68" t="n">
         <v>78526</v>
@@ -8174,10 +8174,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533584</v>
+        <v>533270</v>
       </c>
       <c r="R68" t="n">
-        <v>7209323</v>
+        <v>7209571</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8246,10 +8246,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119536686</v>
+        <v>119536961</v>
       </c>
       <c r="B69" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8258,25 +8258,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533432</v>
+        <v>533584</v>
       </c>
       <c r="R69" t="n">
-        <v>7209492</v>
+        <v>7209323</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8358,10 +8358,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119536687</v>
+        <v>119536937</v>
       </c>
       <c r="B70" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8370,25 +8370,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8398,10 +8398,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533574</v>
+        <v>533428</v>
       </c>
       <c r="R70" t="n">
-        <v>7209350</v>
+        <v>7209500</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8470,10 +8470,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119536937</v>
+        <v>119536522</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8482,25 +8482,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533428</v>
+        <v>533570</v>
       </c>
       <c r="R71" t="n">
-        <v>7209500</v>
+        <v>7209339</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9477,10 +9477,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119536358</v>
+        <v>119536032</v>
       </c>
       <c r="B80" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9493,34 +9493,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533584</v>
+        <v>533461</v>
       </c>
       <c r="R80" t="n">
-        <v>7209327</v>
+        <v>7209454</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9552,7 +9557,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9562,7 +9567,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9589,10 +9594,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119536809</v>
+        <v>119536358</v>
       </c>
       <c r="B81" t="n">
-        <v>90580</v>
+        <v>79608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9605,21 +9610,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9629,10 +9634,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533337</v>
+        <v>533584</v>
       </c>
       <c r="R81" t="n">
-        <v>7209483</v>
+        <v>7209327</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9664,7 +9669,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9674,7 +9679,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9701,10 +9706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119536810</v>
+        <v>119536008</v>
       </c>
       <c r="B82" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9717,21 +9722,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9741,10 +9746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533364</v>
+        <v>533393</v>
       </c>
       <c r="R82" t="n">
-        <v>7209460</v>
+        <v>7209501</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9776,7 +9781,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9786,7 +9791,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9813,10 +9818,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119536032</v>
+        <v>119536011</v>
       </c>
       <c r="B83" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9829,39 +9834,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533461</v>
+        <v>533572</v>
       </c>
       <c r="R83" t="n">
-        <v>7209454</v>
+        <v>7209398</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9930,10 +9930,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119536008</v>
+        <v>119536248</v>
       </c>
       <c r="B84" t="n">
-        <v>90562</v>
+        <v>91339</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9942,25 +9942,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533393</v>
+        <v>533570</v>
       </c>
       <c r="R84" t="n">
-        <v>7209501</v>
+        <v>7209329</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10042,10 +10042,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119536011</v>
+        <v>119535971</v>
       </c>
       <c r="B85" t="n">
-        <v>90562</v>
+        <v>74638</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10058,21 +10058,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10082,10 +10082,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533572</v>
+        <v>533287</v>
       </c>
       <c r="R85" t="n">
-        <v>7209398</v>
+        <v>7209579</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10154,10 +10154,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119536794</v>
+        <v>119537132</v>
       </c>
       <c r="B86" t="n">
-        <v>90576</v>
+        <v>79642</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10166,25 +10166,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533582</v>
+        <v>533301</v>
       </c>
       <c r="R86" t="n">
-        <v>7209319</v>
+        <v>7209573</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10266,10 +10266,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119536616</v>
+        <v>119536809</v>
       </c>
       <c r="B87" t="n">
-        <v>74633</v>
+        <v>90580</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10282,21 +10282,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>310</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533429</v>
+        <v>533337</v>
       </c>
       <c r="R87" t="n">
-        <v>7209490</v>
+        <v>7209483</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10378,10 +10378,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119536248</v>
+        <v>119536810</v>
       </c>
       <c r="B88" t="n">
-        <v>91339</v>
+        <v>90580</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10390,25 +10390,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10418,10 +10418,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533570</v>
+        <v>533364</v>
       </c>
       <c r="R88" t="n">
-        <v>7209329</v>
+        <v>7209460</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10490,7 +10490,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119536921</v>
+        <v>119536936</v>
       </c>
       <c r="B89" t="n">
         <v>78526</v>
@@ -10530,10 +10530,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533273</v>
+        <v>533437</v>
       </c>
       <c r="R89" t="n">
-        <v>7209584</v>
+        <v>7209486</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10602,10 +10602,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119536940</v>
+        <v>119536794</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10618,21 +10618,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10642,10 +10642,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533450</v>
+        <v>533582</v>
       </c>
       <c r="R90" t="n">
-        <v>7209464</v>
+        <v>7209319</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10714,10 +10714,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119537132</v>
+        <v>119536616</v>
       </c>
       <c r="B91" t="n">
-        <v>79642</v>
+        <v>74633</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10726,25 +10726,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6463</v>
+        <v>310</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10754,10 +10754,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533301</v>
+        <v>533429</v>
       </c>
       <c r="R91" t="n">
-        <v>7209573</v>
+        <v>7209490</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10826,7 +10826,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119536936</v>
+        <v>119536921</v>
       </c>
       <c r="B92" t="n">
         <v>78526</v>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533437</v>
+        <v>533273</v>
       </c>
       <c r="R92" t="n">
-        <v>7209486</v>
+        <v>7209584</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10938,10 +10938,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119535971</v>
+        <v>119536940</v>
       </c>
       <c r="B93" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533287</v>
+        <v>533450</v>
       </c>
       <c r="R93" t="n">
-        <v>7209579</v>
+        <v>7209464</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11050,10 +11050,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119536708</v>
+        <v>119536351</v>
       </c>
       <c r="B94" t="n">
-        <v>57459</v>
+        <v>79608</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11066,38 +11066,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533244</v>
+        <v>533312</v>
       </c>
       <c r="R94" t="n">
-        <v>7209556</v>
+        <v>7209566</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11129,7 +11125,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11139,7 +11135,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11166,10 +11162,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119536351</v>
+        <v>119536930</v>
       </c>
       <c r="B95" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11182,21 +11178,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11206,10 +11202,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533312</v>
+        <v>533337</v>
       </c>
       <c r="R95" t="n">
-        <v>7209566</v>
+        <v>7209481</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11241,7 +11237,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11251,7 +11247,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11278,7 +11274,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119536955</v>
+        <v>119536929</v>
       </c>
       <c r="B96" t="n">
         <v>78526</v>
@@ -11318,10 +11314,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533595</v>
+        <v>533307</v>
       </c>
       <c r="R96" t="n">
-        <v>7209370</v>
+        <v>7209487</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11353,7 +11349,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11363,7 +11359,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11390,10 +11386,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119536037</v>
+        <v>119536955</v>
       </c>
       <c r="B97" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11406,39 +11402,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533483</v>
+        <v>533595</v>
       </c>
       <c r="R97" t="n">
-        <v>7209490</v>
+        <v>7209370</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11470,7 +11461,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11480,7 +11471,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11507,10 +11498,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119536769</v>
+        <v>119536708</v>
       </c>
       <c r="B98" t="n">
-        <v>90558</v>
+        <v>57459</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11523,34 +11514,38 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1108</v>
+        <v>103022</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>533560</v>
+        <v>533244</v>
       </c>
       <c r="R98" t="n">
-        <v>7209301</v>
+        <v>7209556</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11582,7 +11577,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11592,7 +11587,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11619,10 +11614,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119536930</v>
+        <v>119536769</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11635,21 +11630,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11659,10 +11654,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533337</v>
+        <v>533560</v>
       </c>
       <c r="R99" t="n">
-        <v>7209481</v>
+        <v>7209301</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11694,7 +11689,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11704,7 +11699,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11731,10 +11726,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119536929</v>
+        <v>119536037</v>
       </c>
       <c r="B100" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11747,34 +11742,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533307</v>
+        <v>533483</v>
       </c>
       <c r="R100" t="n">
-        <v>7209487</v>
+        <v>7209490</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11843,10 +11843,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119536699</v>
+        <v>119536029</v>
       </c>
       <c r="B101" t="n">
-        <v>77463</v>
+        <v>57310</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11859,34 +11859,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533286</v>
+        <v>533270</v>
       </c>
       <c r="R101" t="n">
-        <v>7209578</v>
+        <v>7209571</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11918,7 +11926,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11928,7 +11936,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11955,10 +11963,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119537030</v>
+        <v>119536506</v>
       </c>
       <c r="B102" t="n">
-        <v>82305</v>
+        <v>90846</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11971,21 +11979,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11995,10 +12003,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533330</v>
+        <v>533574</v>
       </c>
       <c r="R102" t="n">
-        <v>7209551</v>
+        <v>7209341</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12030,7 +12038,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12040,7 +12048,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12067,10 +12075,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119536506</v>
+        <v>119536960</v>
       </c>
       <c r="B103" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12083,21 +12091,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12107,10 +12115,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533574</v>
+        <v>533570</v>
       </c>
       <c r="R103" t="n">
-        <v>7209341</v>
+        <v>7209329</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12142,7 +12150,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12152,7 +12160,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12179,10 +12187,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119536969</v>
+        <v>119537030</v>
       </c>
       <c r="B104" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12195,21 +12203,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12219,10 +12227,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>533475</v>
+        <v>533330</v>
       </c>
       <c r="R104" t="n">
-        <v>7209286</v>
+        <v>7209551</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12254,7 +12262,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12264,7 +12272,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12291,7 +12299,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119536933</v>
+        <v>119536969</v>
       </c>
       <c r="B105" t="n">
         <v>78526</v>
@@ -12331,10 +12339,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>533413</v>
+        <v>533475</v>
       </c>
       <c r="R105" t="n">
-        <v>7209495</v>
+        <v>7209286</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12366,7 +12374,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12376,7 +12384,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12403,7 +12411,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119536960</v>
+        <v>119536933</v>
       </c>
       <c r="B106" t="n">
         <v>78526</v>
@@ -12443,10 +12451,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533570</v>
+        <v>533413</v>
       </c>
       <c r="R106" t="n">
-        <v>7209329</v>
+        <v>7209495</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12478,7 +12486,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12488,7 +12496,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12515,10 +12523,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119536029</v>
+        <v>119536699</v>
       </c>
       <c r="B107" t="n">
-        <v>57310</v>
+        <v>77463</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12531,42 +12539,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533270</v>
+        <v>533286</v>
       </c>
       <c r="R107" t="n">
-        <v>7209571</v>
+        <v>7209578</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14105,7 +14105,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119536952</v>
+        <v>119536943</v>
       </c>
       <c r="B121" t="n">
         <v>78526</v>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533571</v>
+        <v>533473</v>
       </c>
       <c r="R121" t="n">
-        <v>7209383</v>
+        <v>7209486</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14180,7 +14180,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14217,10 +14217,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119536815</v>
+        <v>119536923</v>
       </c>
       <c r="B122" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14233,21 +14233,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14257,10 +14257,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533572</v>
+        <v>533284</v>
       </c>
       <c r="R122" t="n">
-        <v>7209398</v>
+        <v>7209569</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14441,7 +14441,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119536943</v>
+        <v>119536952</v>
       </c>
       <c r="B124" t="n">
         <v>78526</v>
@@ -14481,10 +14481,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>533473</v>
+        <v>533571</v>
       </c>
       <c r="R124" t="n">
-        <v>7209486</v>
+        <v>7209383</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14553,10 +14553,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119536923</v>
+        <v>119536815</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14569,21 +14569,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533284</v>
+        <v>533572</v>
       </c>
       <c r="R125" t="n">
-        <v>7209569</v>
+        <v>7209398</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15113,10 +15113,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119536489</v>
+        <v>119536964</v>
       </c>
       <c r="B130" t="n">
-        <v>74450</v>
+        <v>78526</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15125,25 +15125,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15153,10 +15153,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533408</v>
+        <v>533550</v>
       </c>
       <c r="R130" t="n">
-        <v>7209505</v>
+        <v>7209252</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15225,7 +15225,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119536938</v>
+        <v>119536932</v>
       </c>
       <c r="B131" t="n">
         <v>78526</v>
@@ -15265,10 +15265,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533435</v>
+        <v>533391</v>
       </c>
       <c r="R131" t="n">
-        <v>7209492</v>
+        <v>7209500</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15454,10 +15454,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119536964</v>
+        <v>119536489</v>
       </c>
       <c r="B133" t="n">
-        <v>78526</v>
+        <v>74450</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15466,25 +15466,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15494,10 +15494,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>533550</v>
+        <v>533408</v>
       </c>
       <c r="R133" t="n">
-        <v>7209252</v>
+        <v>7209505</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15566,7 +15566,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119536932</v>
+        <v>119536938</v>
       </c>
       <c r="B134" t="n">
         <v>78526</v>
@@ -15606,10 +15606,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>533391</v>
+        <v>533435</v>
       </c>
       <c r="R134" t="n">
-        <v>7209500</v>
+        <v>7209492</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17363,10 +17363,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119536041</v>
+        <v>119536474</v>
       </c>
       <c r="B150" t="n">
-        <v>57310</v>
+        <v>74643</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17379,39 +17379,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>533344</v>
+        <v>533343</v>
       </c>
       <c r="R150" t="n">
-        <v>7209427</v>
+        <v>7209486</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -17443,7 +17438,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17453,7 +17448,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17480,10 +17475,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119536038</v>
+        <v>119536942</v>
       </c>
       <c r="B151" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17496,39 +17491,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533510</v>
+        <v>533471</v>
       </c>
       <c r="R151" t="n">
-        <v>7209427</v>
+        <v>7209472</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -17560,7 +17550,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17570,7 +17560,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17597,10 +17587,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119536356</v>
+        <v>119536962</v>
       </c>
       <c r="B152" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17613,21 +17603,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17637,10 +17627,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533430</v>
+        <v>533550</v>
       </c>
       <c r="R152" t="n">
-        <v>7209489</v>
+        <v>7209319</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -17672,7 +17662,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17682,7 +17672,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17709,10 +17699,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119536474</v>
+        <v>119536356</v>
       </c>
       <c r="B153" t="n">
-        <v>74643</v>
+        <v>79608</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17725,21 +17715,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17749,10 +17739,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533343</v>
+        <v>533430</v>
       </c>
       <c r="R153" t="n">
-        <v>7209486</v>
+        <v>7209489</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -17784,7 +17774,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17794,7 +17784,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17821,10 +17811,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119536942</v>
+        <v>119536041</v>
       </c>
       <c r="B154" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17837,34 +17827,39 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533471</v>
+        <v>533344</v>
       </c>
       <c r="R154" t="n">
-        <v>7209472</v>
+        <v>7209427</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17896,7 +17891,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17906,7 +17901,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17933,10 +17928,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119536962</v>
+        <v>119536038</v>
       </c>
       <c r="B155" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17949,34 +17944,39 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Hällmyran, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533550</v>
+        <v>533510</v>
       </c>
       <c r="R155" t="n">
-        <v>7209319</v>
+        <v>7209427</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18008,7 +18008,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD155" t="b">
